--- a/excel_routes/route_MED_HMB_threats.xlsx
+++ b/excel_routes/route_MED_HMB_threats.xlsx
@@ -48,14 +48,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF3CD"/>
-        <bgColor rgb="00FFF3CD"/>
+        <fgColor rgb="00D4EDDA"/>
+        <bgColor rgb="00D4EDDA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D4EDDA"/>
-        <bgColor rgb="00D4EDDA"/>
+        <fgColor rgb="00FFF3CD"/>
+        <bgColor rgb="00FFF3CD"/>
       </patternFill>
     </fill>
   </fills>
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -532,7 +532,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>09-JUL-26</t>
+          <t>02-JUL-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -542,30 +542,30 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-696</t>
+          <t>flyadeal F3-771</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>753</v>
+        <v>509</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-223</v>
+        <v>-467</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>-16</v>
+        <v>15</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -577,7 +577,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>09-JUL-26</t>
+          <t>02-JUL-26</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -587,28 +587,28 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-676</t>
+          <t>flynas XY-793</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>833</v>
+        <v>539</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-143</v>
+        <v>-437</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J3" s="4" t="inlineStr">
+        <v>15</v>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -632,17 +632,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-640</t>
+          <t>EgyptAir MS-696</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>833</v>
+        <v>753</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-143</v>
+        <v>-223</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>46</v>
@@ -655,7 +655,7 @@
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -677,17 +677,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-694</t>
+          <t>EgyptAir MS-676</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>923</v>
+        <v>833</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-53</v>
+        <v>-143</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>46</v>
@@ -698,12 +698,192 @@
       <c r="I5" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J5" s="4" t="inlineStr">
+      <c r="J5" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>09-JUL-26</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>SM-490</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-640</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>833</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>976</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>-143</v>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I6" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>24-SEP-26</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>SM-490</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-793</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>429</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>898</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>-469</v>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H7" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I7" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>24-SEP-26</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>SM-490</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-576</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>429</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>898</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>-469</v>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I8" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>24-SEP-26</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>SM-490</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-775</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>439</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>898</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>-459</v>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H9" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I9" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>SAR</t>
         </is>

--- a/excel_routes/route_MED_HMB_threats.xlsx
+++ b/excel_routes/route_MED_HMB_threats.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -622,7 +622,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>09-JUL-26</t>
+          <t>02-JUL-26</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -632,30 +632,30 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-696</t>
+          <t>flyadeal F3-775</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>753</v>
+        <v>819</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-223</v>
+        <v>-157</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J4" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>-10</v>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -677,17 +677,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-676</t>
+          <t>EgyptAir MS-696</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>833</v>
+        <v>753</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-143</v>
+        <v>-223</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>46</v>
@@ -698,9 +698,9 @@
       <c r="I5" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -722,7 +722,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-640</t>
+          <t>EgyptAir MS-676</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
@@ -757,7 +757,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>24-SEP-26</t>
+          <t>09-JUL-26</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -767,26 +767,26 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-793</t>
+          <t>EgyptAir MS-640</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>429</v>
+        <v>833</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>898</v>
+        <v>976</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-469</v>
+        <v>-143</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="H7" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>15</v>
+        <v>-16</v>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
@@ -812,26 +812,26 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-576</t>
+          <t>flyadeal F3-775</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>429</v>
+        <v>616</v>
       </c>
       <c r="E8" s="2" t="n">
         <v>898</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-469</v>
+        <v>-282</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H8" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
@@ -857,33 +857,78 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-775</t>
+          <t>flynas XY-793</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>439</v>
+        <v>619</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>898</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-459</v>
+        <v>-279</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="H9" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-10</v>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>24-SEP-26</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>SM-490</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-576</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>619</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>898</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>-279</v>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I10" s="2" t="n">
+        <v>-10</v>
+      </c>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>SAR</t>
         </is>

--- a/excel_routes/route_MED_HMB_threats.xlsx
+++ b/excel_routes/route_MED_HMB_threats.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -622,7 +622,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>02-JUL-26</t>
+          <t>09-JUL-26</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -632,30 +632,30 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-775</t>
+          <t>EgyptAir MS-696</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>819</v>
+        <v>753</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-157</v>
+        <v>-223</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -677,17 +677,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-696</t>
+          <t>EgyptAir MS-676</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>753</v>
+        <v>833</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-223</v>
+        <v>-143</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>46</v>
@@ -698,9 +698,9 @@
       <c r="I5" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J5" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -722,7 +722,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-676</t>
+          <t>EgyptAir MS-640</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
@@ -757,7 +757,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>09-JUL-26</t>
+          <t>24-SEP-26</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -767,26 +767,26 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-640</t>
+          <t>flynas XY-793</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>833</v>
+        <v>429</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>976</v>
+        <v>898</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-143</v>
+        <v>-469</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="H7" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>-16</v>
+        <v>15</v>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
@@ -812,26 +812,26 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-775</t>
+          <t>flynas XY-576</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>616</v>
+        <v>429</v>
       </c>
       <c r="E8" s="2" t="n">
         <v>898</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-282</v>
+        <v>-469</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H8" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
@@ -857,78 +857,33 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-793</t>
+          <t>flyadeal F3-775</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>619</v>
+        <v>439</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>898</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-279</v>
+        <v>-459</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="H9" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J9" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>15</v>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>24-SEP-26</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>SM-490</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>flynas XY-576</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="n">
-        <v>619</v>
-      </c>
-      <c r="E10" s="2" t="n">
-        <v>898</v>
-      </c>
-      <c r="F10" s="2" t="n">
-        <v>-279</v>
-      </c>
-      <c r="G10" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="H10" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I10" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J10" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>SAR</t>
         </is>

--- a/excel_routes/route_MED_HMB_threats.xlsx
+++ b/excel_routes/route_MED_HMB_threats.xlsx
@@ -542,26 +542,26 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-771</t>
+          <t>flynas XY-793</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>509</v>
+        <v>729</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-467</v>
+        <v>-247</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>15</v>
+        <v>-10</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
@@ -587,26 +587,26 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-793</t>
+          <t>flyadeal F3-771</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>539</v>
+        <v>819</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-437</v>
+        <v>-157</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>15</v>
+        <v>-10</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>

--- a/excel_routes/route_MED_HMB_threats.xlsx
+++ b/excel_routes/route_MED_HMB_threats.xlsx
@@ -542,26 +542,26 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-793</t>
+          <t>flyadeal F3-771</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>729</v>
+        <v>469</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>976</v>
+        <v>1054</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-247</v>
+        <v>-585</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>-10</v>
+        <v>15</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
@@ -587,26 +587,26 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-771</t>
+          <t>flynas XY-793</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>819</v>
+        <v>619</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>976</v>
+        <v>1054</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-157</v>
+        <v>-435</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>-10</v>
+        <v>15</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
@@ -636,13 +636,13 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>753</v>
+        <v>790</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-223</v>
+        <v>-186</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>46</v>
@@ -681,13 +681,13 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>833</v>
+        <v>870</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-143</v>
+        <v>-106</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>46</v>
@@ -726,13 +726,13 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>833</v>
+        <v>870</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-143</v>
+        <v>-106</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>46</v>

--- a/excel_routes/route_MED_HMB_threats.xlsx
+++ b/excel_routes/route_MED_HMB_threats.xlsx
@@ -33,7 +33,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -50,12 +50,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00D4EDDA"/>
         <bgColor rgb="00D4EDDA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF3CD"/>
-        <bgColor rgb="00FFF3CD"/>
       </patternFill>
     </fill>
   </fills>
@@ -77,7 +71,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -86,9 +80,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -456,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -542,26 +533,26 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-771</t>
+          <t>EgyptAir MS-676</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>469</v>
+        <v>620</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>1054</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-585</v>
+        <v>-434</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
@@ -587,26 +578,26 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-793</t>
+          <t>EgyptAir MS-694</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>1054</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-435</v>
+        <v>-434</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
@@ -622,7 +613,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>09-JUL-26</t>
+          <t>02-JUL-26</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -636,26 +627,26 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>790</v>
+        <v>620</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>976</v>
+        <v>1054</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-186</v>
+        <v>-434</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J4" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>7</v>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -681,22 +672,22 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>870</v>
+        <v>620</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-106</v>
+        <v>-356</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>-16</v>
+        <v>7</v>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
@@ -722,26 +713,26 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-640</t>
+          <t>EgyptAir MS-694</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>870</v>
+        <v>620</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-106</v>
+        <v>-356</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>-16</v>
+        <v>7</v>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
@@ -757,7 +748,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>24-SEP-26</t>
+          <t>09-JUL-26</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -767,26 +758,26 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-793</t>
+          <t>EgyptAir MS-696</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>429</v>
+        <v>620</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>898</v>
+        <v>976</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-469</v>
+        <v>-356</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="H7" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
@@ -802,7 +793,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>24-SEP-26</t>
+          <t>16-JUL-26</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -812,26 +803,26 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-576</t>
+          <t>EgyptAir MS-676</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>429</v>
+        <v>701</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>898</v>
+        <v>682</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-469</v>
+        <v>19</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="H8" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>15</v>
+        <v>-16</v>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
@@ -861,13 +852,13 @@
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>439</v>
+        <v>409</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>898</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-459</v>
+        <v>-489</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>15</v>
@@ -884,6 +875,96 @@
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>24-SEP-26</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>SM-490</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-771</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>409</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>898</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>-489</v>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I10" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>24-SEP-26</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>SM-490</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-793</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>434</v>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>898</v>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>-464</v>
+      </c>
+      <c r="G11" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H11" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I11" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>SAR</t>
         </is>
